--- a/data/trans_orig/cron_prev_index-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/cron_prev_index-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de cronicidad física en base a la prevalencia</t>
+          <t>Índice de cronicidad física en base a la prevalencia (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,49</t>
+          <t>0,38; 0,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -726,17 +726,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,63</t>
+          <t>0,49; 0,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 0,79</t>
+          <t>0,63; 0,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,72</t>
+          <t>0,56; 0,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -746,22 +746,22 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,8</t>
+          <t>0,62; 0,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,96</t>
+          <t>0,68; 0,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,58</t>
+          <t>0,5; 0,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,71</t>
+          <t>0,61; 0,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,85</t>
+          <t>0,71; 0,85</t>
         </is>
       </c>
     </row>
@@ -856,27 +856,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,53</t>
+          <t>0,42; 0,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,59</t>
+          <t>0,46; 0,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,58</t>
+          <t>0,47; 0,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,65</t>
+          <t>0,23; 0,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,75</t>
+          <t>0,63; 0,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,76</t>
+          <t>0,63; 0,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,63</t>
+          <t>0,53; 0,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,65</t>
+          <t>0,56; 0,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 0,7</t>
+          <t>0,41; 0,7</t>
         </is>
       </c>
     </row>
@@ -996,17 +996,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,49</t>
+          <t>0,37; 0,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,55</t>
+          <t>0,41; 0,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,57</t>
+          <t>0,44; 0,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,74</t>
+          <t>0,6; 0,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,71</t>
+          <t>0,56; 0,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 0,7</t>
+          <t>0,55; 0,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,98</t>
+          <t>0,61; 2,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,59</t>
+          <t>0,5; 0,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,61</t>
+          <t>0,51; 0,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,65</t>
+          <t>0,65; 1,62</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 0,63</t>
+          <t>0,5; 0,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,56</t>
+          <t>0,46; 0,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 0,69</t>
+          <t>0,56; 0,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 0,68</t>
+          <t>0,56; 0,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,81; 0,94</t>
+          <t>0,82; 0,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,61</t>
+          <t>0,52; 0,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1291,32 +1291,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,69</t>
+          <t>0,49; 0,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,62; 0,68</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,67; 0,74</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
           <t>0,62; 0,69</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,67; 0,75</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,62; 0,69</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,3</t>
+          <t>0,78; 1,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,57</t>
+          <t>0,53; 0,58</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,0</t>
+          <t>0,69; 0,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/cron_prev_index-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/cron_prev_index-Habitat-trans_orig.xlsx
@@ -663,27 +663,27 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>0,7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,64</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,75</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>0,71</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,64</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,71</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>0,9</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,79</t>
+          <t>0,81</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,63</t>
+          <t>0,48; 0,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,42 +736,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,71</t>
+          <t>0,57; 0,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,84</t>
+          <t>0,67; 0,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,79</t>
+          <t>0,62; 0,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 0,95</t>
+          <t>0,83; 0,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,59</t>
+          <t>0,49; 0,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,72</t>
+          <t>0,6; 0,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,69</t>
+          <t>0,57; 0,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 0,85</t>
+          <t>0,75; 0,86</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,63</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,68</t>
         </is>
       </c>
     </row>
@@ -861,22 +861,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,58</t>
+          <t>0,46; 0,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,57</t>
+          <t>0,46; 0,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,65</t>
+          <t>0,57; 0,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,76</t>
+          <t>0,62; 0,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,22 +886,22 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,76</t>
+          <t>0,62; 0,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 0,8</t>
+          <t>0,68; 0,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,62</t>
+          <t>0,54; 0,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,66</t>
+          <t>0,56; 0,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,7</t>
+          <t>0,64; 0,72</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>0,68</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,55</t>
+          <t>0,42; 0,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 0,79</t>
+          <t>0,62; 0,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 0,75</t>
+          <t>0,59; 0,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,7</t>
+          <t>0,55; 0,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,06</t>
+          <t>0,61; 0,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>0,51; 0,61</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>0,51; 0,62</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>0,52; 0,62</t>
-        </is>
-      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,62</t>
+          <t>0,63; 0,73</t>
         </is>
       </c>
     </row>
@@ -1083,47 +1083,47 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>0,66</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,62</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,76</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0,62</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0,85</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0,54</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0,67</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,62</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0,56</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,76</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,62</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,87</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0,67</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>0,56</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,51</t>
+          <t>0,4; 0,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,63</t>
+          <t>0,5; 0,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 0,74</t>
+          <t>0,59; 0,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 0,94</t>
+          <t>0,8; 0,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 0,83</t>
+          <t>0,72; 0,81</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,73</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,69</t>
+          <t>0,63; 0,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,68</t>
+          <t>0,62; 0,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,29</t>
+          <t>0,76; 0,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,61</t>
+          <t>0,57; 0,61</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,98</t>
+          <t>0,71; 0,75</t>
         </is>
       </c>
     </row>
